--- a/reports/BSH_Detayli_Fiyat_Raporu.xlsx
+++ b/reports/BSH_Detayli_Fiyat_Raporu.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="171">
   <si>
     <t>Marka</t>
   </si>
@@ -40,9 +40,111 @@
     <t>Bosch</t>
   </si>
   <si>
+    <t>Bulaşık Makinesi</t>
+  </si>
+  <si>
+    <t>Buzdolabı</t>
+  </si>
+  <si>
+    <t>Klima</t>
+  </si>
+  <si>
     <t>Çamaşır Makinesi</t>
   </si>
   <si>
+    <t>SMV4IMX62T</t>
+  </si>
+  <si>
+    <t>SMS6EMI63T</t>
+  </si>
+  <si>
+    <t>SMP6ENC60T</t>
+  </si>
+  <si>
+    <t>SMS6ENW60T</t>
+  </si>
+  <si>
+    <t>SMS6ENY60T</t>
+  </si>
+  <si>
+    <t>SMS6ENB60T</t>
+  </si>
+  <si>
+    <t>SMS4HMY62T</t>
+  </si>
+  <si>
+    <t>SMS6ECI83T</t>
+  </si>
+  <si>
+    <t>SMI6EKS81T</t>
+  </si>
+  <si>
+    <t>SMV6ECX86Q</t>
+  </si>
+  <si>
+    <t>SMS8YDI82T</t>
+  </si>
+  <si>
+    <t>SMI8ZDS81T</t>
+  </si>
+  <si>
+    <t>KGN76CXE0N</t>
+  </si>
+  <si>
+    <t>KGP76AWC0N</t>
+  </si>
+  <si>
+    <t>KDN86AWE1N</t>
+  </si>
+  <si>
+    <t>KGN86AID2N</t>
+  </si>
+  <si>
+    <t>KGA76PIE0N</t>
+  </si>
+  <si>
+    <t>KGP76AIC0N</t>
+  </si>
+  <si>
+    <t>KDN86AID1N</t>
+  </si>
+  <si>
+    <t>KGP86FWC0N</t>
+  </si>
+  <si>
+    <t>KGP86FIC0N</t>
+  </si>
+  <si>
+    <t>KGP86AXB0N</t>
+  </si>
+  <si>
+    <t>KFN96VPEA</t>
+  </si>
+  <si>
+    <t>KBN96ADD0</t>
+  </si>
+  <si>
+    <t>ASX09VW32N</t>
+  </si>
+  <si>
+    <t>ASX12VW32N</t>
+  </si>
+  <si>
+    <t>ASX12XB32N</t>
+  </si>
+  <si>
+    <t>ASX18VW32N</t>
+  </si>
+  <si>
+    <t>ASX18XB32N</t>
+  </si>
+  <si>
+    <t>ASX24VW32N</t>
+  </si>
+  <si>
+    <t>WGA254A0TR</t>
+  </si>
+  <si>
     <t>WGK242Z0TR</t>
   </si>
   <si>
@@ -79,6 +181,72 @@
     <t>WGK264ZRTR</t>
   </si>
   <si>
+    <t>Serie 6 Tam Ankastre Bulaşık Makinesi 60 cm</t>
+  </si>
+  <si>
+    <t>Serie 6 Solo Bulaşık Makinesi 60 cm Kolay Temizlenebilir Inox</t>
+  </si>
+  <si>
+    <t>Serie 6 Solo Bulaşık Makinesi 60 cm Kolay Temizlenebilir Siyah Inox</t>
+  </si>
+  <si>
+    <t>Serie 6 Solo Bulaşık Makinesi 60 cm Beyaz</t>
+  </si>
+  <si>
+    <t>Serie 6 Solo Bulaşık Makinesi 60 cm</t>
+  </si>
+  <si>
+    <t>Serie 6 Solo Bulaşık Makinesi 60 cm Siyah</t>
+  </si>
+  <si>
+    <t>Serie 6 Yarı Ankastre Bulaşık Makinesi 60 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>Serie 8 Solo Bulaşık Makinesi 60 cm Kolay Temizlenebilir Inox</t>
+  </si>
+  <si>
+    <t>Serie 8 Yarı Ankastre Bulaşık Makinesi 60 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>Serie 6 Alttan Donduruculu Buzdolabı 186 x 75 cm Parmak izi bırakmayan siyah inoks</t>
+  </si>
+  <si>
+    <t>Serie 8 Alttan Donduruculu Buzdolabı 186 x 75 cm Beyaz, Total No Frost</t>
+  </si>
+  <si>
+    <t>Serie 6 Üstten Donduruculu Buzdolabı 186 x 86 cm Beyaz, Total No Frost</t>
+  </si>
+  <si>
+    <t>Serie 6 Alttan Donduruculu Buzdolabı 186 x 86 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>Serie 8 Alttan Donduruculu Buzdolabı 186 x 75 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>Serie 6 Üstten Donduruculu Buzdolabı 186 x 86 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>Serie 8 Alttan Donduruculu Buzdolabı 186 x 86 cm Beyaz, Total No Frost</t>
+  </si>
+  <si>
+    <t>Serie 8 Alttan Donduruculu Buzdolabı 186 x 86 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>Serie 8 Alttan Donduruculu Buzdolabı 186 x 86 cm Parmak izi bırakmayan siyah inoks</t>
+  </si>
+  <si>
+    <t>Serie 4 Gardırop Tipi Buzdolabı 183 x 90.5 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>Serie 6 Alttan Donduruculu Ankastre Buzdolabı 193.5 x 70.8 cm softClosing Düz Menteşe</t>
+  </si>
+  <si>
+    <t>Klima, Ev Tipi</t>
+  </si>
+  <si>
+    <t>Bosch 10 kg 1200 Devir Çamaşır Makinesi</t>
+  </si>
+  <si>
     <t>Serie 6 Çamaşır Makinesi 9 kg maks. 1200 dev./dak.</t>
   </si>
   <si>
@@ -106,40 +274,259 @@
     <t>Stokta Var</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:38</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:34</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:44</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:24</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:54</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:25</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:40</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:46</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:20:00</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:29</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:33</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:36</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:59</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:27</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:50</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:41</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:52</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:31</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:42</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:42</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:56</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:22</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:48</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:38</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:02</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:48</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:50</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:53</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:58</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:04</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:52</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:08</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:47</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:06</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:00</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:55</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:20:11</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:19</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:20:13</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:13</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:20:16</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:21</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:20:17</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:12</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:20:08</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:17</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:20:10</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:25:15</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:16:14</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:44</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:28</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:12</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:50</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:23</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:11</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:59</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:30</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:09</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:46</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:17</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:04</t>
+  </si>
+  <si>
     <t>2026-07-01 16:56:02</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:32</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:00</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:49</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:19</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:16</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:57</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:26</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:02</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:47</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:33</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:18</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:55</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:14</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:06</t>
+  </si>
+  <si>
     <t>2026-07-01 16:56:00</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:24</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:23:58</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:53</t>
   </si>
   <si>
+    <t>2026-07-01 17:19:21</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:14</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:52</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:19:16</t>
+  </si>
+  <si>
+    <t>2026-07-01 17:24:07</t>
   </si>
 </sst>
 </file>
@@ -497,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -531,19 +918,19 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="E2">
-        <v>44510</v>
+        <v>44350</v>
       </c>
       <c r="F2" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -554,19 +941,19 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="E3">
-        <v>46040</v>
+        <v>44350</v>
       </c>
       <c r="F3" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G3" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -577,19 +964,19 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="E4">
-        <v>46210</v>
+        <v>44430</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G4" t="s">
-        <v>32</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -600,19 +987,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E5">
-        <v>46440</v>
+        <v>44430</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -623,19 +1010,19 @@
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E6">
-        <v>46560</v>
+        <v>45080</v>
       </c>
       <c r="F6" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -649,16 +1036,16 @@
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E7">
-        <v>47150</v>
+        <v>45080</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -672,16 +1059,16 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="E8">
-        <v>48310</v>
+        <v>47010</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>36</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -695,16 +1082,16 @@
         <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="E9">
-        <v>48460</v>
+        <v>47010</v>
       </c>
       <c r="F9" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G9" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -718,16 +1105,16 @@
         <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E10">
-        <v>49700</v>
+        <v>47010</v>
       </c>
       <c r="F10" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -738,19 +1125,19 @@
         <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="E11">
-        <v>51090</v>
+        <v>47010</v>
       </c>
       <c r="F11" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -761,19 +1148,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="E12">
-        <v>52660</v>
+        <v>47010</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s">
-        <v>40</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -784,19 +1171,1698 @@
         <v>8</v>
       </c>
       <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13">
+        <v>47010</v>
+      </c>
+      <c r="F13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14">
+        <v>51300</v>
+      </c>
+      <c r="F14" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15">
+        <v>51300</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16">
+        <v>59970</v>
+      </c>
+      <c r="F16" t="s">
+        <v>85</v>
+      </c>
+      <c r="G16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17">
+        <v>59970</v>
+      </c>
+      <c r="F17" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
         <v>20</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18">
+        <v>62580</v>
+      </c>
+      <c r="F18" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19">
+        <v>62580</v>
+      </c>
+      <c r="F19" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20">
+        <v>63200</v>
+      </c>
+      <c r="F20" t="s">
+        <v>85</v>
+      </c>
+      <c r="G20" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21">
+        <v>63200</v>
+      </c>
+      <c r="F21" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>22</v>
+      </c>
+      <c r="D22" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22">
+        <v>66470</v>
+      </c>
+      <c r="F22" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23">
+        <v>66470</v>
+      </c>
+      <c r="F23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24" t="s">
+        <v>63</v>
+      </c>
+      <c r="E24">
+        <v>81510</v>
+      </c>
+      <c r="F24" t="s">
+        <v>85</v>
+      </c>
+      <c r="G24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>23</v>
+      </c>
+      <c r="D25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25">
+        <v>81510</v>
+      </c>
+      <c r="F25" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26">
+        <v>87390</v>
+      </c>
+      <c r="F26" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27">
+        <v>87890</v>
+      </c>
+      <c r="F27" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28">
+        <v>88600</v>
+      </c>
+      <c r="F28" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29">
+        <v>94490</v>
+      </c>
+      <c r="F29" t="s">
+        <v>85</v>
+      </c>
+      <c r="G29" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
         <v>28</v>
       </c>
-      <c r="E13">
+      <c r="D30" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30">
+        <v>94890</v>
+      </c>
+      <c r="F30" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" t="s">
+        <v>29</v>
+      </c>
+      <c r="D31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31">
+        <v>95390</v>
+      </c>
+      <c r="F31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" t="s">
+        <v>30</v>
+      </c>
+      <c r="D32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E32">
+        <v>96750</v>
+      </c>
+      <c r="F32" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" t="s">
+        <v>31</v>
+      </c>
+      <c r="D33" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33">
+        <v>99790</v>
+      </c>
+      <c r="F33" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34">
+        <v>105790</v>
+      </c>
+      <c r="F34" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35">
+        <v>115290</v>
+      </c>
+      <c r="F35" t="s">
+        <v>85</v>
+      </c>
+      <c r="G35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" t="s">
+        <v>73</v>
+      </c>
+      <c r="E36">
+        <v>122990</v>
+      </c>
+      <c r="F36" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E37">
+        <v>127110</v>
+      </c>
+      <c r="F37" t="s">
+        <v>85</v>
+      </c>
+      <c r="G37" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E38">
+        <v>45700</v>
+      </c>
+      <c r="F38" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" t="s">
+        <v>36</v>
+      </c>
+      <c r="D39" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39">
+        <v>45700</v>
+      </c>
+      <c r="F39" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>7</v>
+      </c>
+      <c r="B40" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" t="s">
+        <v>37</v>
+      </c>
+      <c r="D40" t="s">
+        <v>75</v>
+      </c>
+      <c r="E40">
+        <v>50200</v>
+      </c>
+      <c r="F40" t="s">
+        <v>85</v>
+      </c>
+      <c r="G40" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>10</v>
+      </c>
+      <c r="C41" t="s">
+        <v>37</v>
+      </c>
+      <c r="D41" t="s">
+        <v>75</v>
+      </c>
+      <c r="E41">
+        <v>50200</v>
+      </c>
+      <c r="F41" t="s">
+        <v>85</v>
+      </c>
+      <c r="G41" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42">
+        <v>56030</v>
+      </c>
+      <c r="F42" t="s">
+        <v>85</v>
+      </c>
+      <c r="G42" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" t="s">
+        <v>10</v>
+      </c>
+      <c r="C43" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" t="s">
+        <v>75</v>
+      </c>
+      <c r="E43">
+        <v>56030</v>
+      </c>
+      <c r="F43" t="s">
+        <v>85</v>
+      </c>
+      <c r="G43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C44" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" t="s">
+        <v>75</v>
+      </c>
+      <c r="E44">
+        <v>70810</v>
+      </c>
+      <c r="F44" t="s">
+        <v>85</v>
+      </c>
+      <c r="G44" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" t="s">
+        <v>75</v>
+      </c>
+      <c r="E45">
+        <v>70810</v>
+      </c>
+      <c r="F45" t="s">
+        <v>85</v>
+      </c>
+      <c r="G45" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" t="s">
+        <v>40</v>
+      </c>
+      <c r="D46" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46">
+        <v>79070</v>
+      </c>
+      <c r="F46" t="s">
+        <v>85</v>
+      </c>
+      <c r="G46" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47">
+        <v>79070</v>
+      </c>
+      <c r="F47" t="s">
+        <v>85</v>
+      </c>
+      <c r="G47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" t="s">
+        <v>75</v>
+      </c>
+      <c r="E48">
+        <v>85790</v>
+      </c>
+      <c r="F48" t="s">
+        <v>85</v>
+      </c>
+      <c r="G48" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" t="s">
+        <v>41</v>
+      </c>
+      <c r="D49" t="s">
+        <v>75</v>
+      </c>
+      <c r="E49">
+        <v>85790</v>
+      </c>
+      <c r="F49" t="s">
+        <v>85</v>
+      </c>
+      <c r="G49" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>7</v>
+      </c>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" t="s">
+        <v>42</v>
+      </c>
+      <c r="D50" t="s">
+        <v>76</v>
+      </c>
+      <c r="E50">
+        <v>24500</v>
+      </c>
+      <c r="F50" t="s">
+        <v>85</v>
+      </c>
+      <c r="G50" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>43</v>
+      </c>
+      <c r="D51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51">
+        <v>44510</v>
+      </c>
+      <c r="F51" t="s">
+        <v>85</v>
+      </c>
+      <c r="G51" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>43</v>
+      </c>
+      <c r="D52" t="s">
+        <v>77</v>
+      </c>
+      <c r="E52">
+        <v>44510</v>
+      </c>
+      <c r="F52" t="s">
+        <v>85</v>
+      </c>
+      <c r="G52" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>43</v>
+      </c>
+      <c r="D53" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53">
+        <v>44510</v>
+      </c>
+      <c r="F53" t="s">
+        <v>85</v>
+      </c>
+      <c r="G53" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54">
+        <v>46040</v>
+      </c>
+      <c r="F54" t="s">
+        <v>85</v>
+      </c>
+      <c r="G54" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" t="s">
+        <v>78</v>
+      </c>
+      <c r="E55">
+        <v>46040</v>
+      </c>
+      <c r="F55" t="s">
+        <v>85</v>
+      </c>
+      <c r="G55" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>44</v>
+      </c>
+      <c r="D56" t="s">
+        <v>78</v>
+      </c>
+      <c r="E56">
+        <v>46040</v>
+      </c>
+      <c r="F56" t="s">
+        <v>85</v>
+      </c>
+      <c r="G56" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" t="s">
+        <v>79</v>
+      </c>
+      <c r="E57">
+        <v>46210</v>
+      </c>
+      <c r="F57" t="s">
+        <v>85</v>
+      </c>
+      <c r="G57" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>7</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" t="s">
+        <v>45</v>
+      </c>
+      <c r="D58" t="s">
+        <v>79</v>
+      </c>
+      <c r="E58">
+        <v>46210</v>
+      </c>
+      <c r="F58" t="s">
+        <v>85</v>
+      </c>
+      <c r="G58" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>45</v>
+      </c>
+      <c r="D59" t="s">
+        <v>79</v>
+      </c>
+      <c r="E59">
+        <v>46210</v>
+      </c>
+      <c r="F59" t="s">
+        <v>85</v>
+      </c>
+      <c r="G59" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>7</v>
+      </c>
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" t="s">
+        <v>80</v>
+      </c>
+      <c r="E60">
+        <v>46440</v>
+      </c>
+      <c r="F60" t="s">
+        <v>85</v>
+      </c>
+      <c r="G60" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>7</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61">
+        <v>46440</v>
+      </c>
+      <c r="F61" t="s">
+        <v>85</v>
+      </c>
+      <c r="G61" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" t="s">
+        <v>80</v>
+      </c>
+      <c r="E62">
+        <v>46440</v>
+      </c>
+      <c r="F62" t="s">
+        <v>85</v>
+      </c>
+      <c r="G62" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63">
+        <v>46560</v>
+      </c>
+      <c r="F63" t="s">
+        <v>85</v>
+      </c>
+      <c r="G63" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64" t="s">
+        <v>80</v>
+      </c>
+      <c r="E64">
+        <v>46560</v>
+      </c>
+      <c r="F64" t="s">
+        <v>85</v>
+      </c>
+      <c r="G64" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65">
+        <v>46560</v>
+      </c>
+      <c r="F65" t="s">
+        <v>85</v>
+      </c>
+      <c r="G65" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>48</v>
+      </c>
+      <c r="D66" t="s">
+        <v>81</v>
+      </c>
+      <c r="E66">
+        <v>47150</v>
+      </c>
+      <c r="F66" t="s">
+        <v>85</v>
+      </c>
+      <c r="G66" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>48</v>
+      </c>
+      <c r="D67" t="s">
+        <v>81</v>
+      </c>
+      <c r="E67">
+        <v>47150</v>
+      </c>
+      <c r="F67" t="s">
+        <v>85</v>
+      </c>
+      <c r="G67" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>48</v>
+      </c>
+      <c r="D68" t="s">
+        <v>81</v>
+      </c>
+      <c r="E68">
+        <v>47150</v>
+      </c>
+      <c r="F68" t="s">
+        <v>85</v>
+      </c>
+      <c r="G68" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69" t="s">
+        <v>82</v>
+      </c>
+      <c r="E69">
+        <v>48310</v>
+      </c>
+      <c r="F69" t="s">
+        <v>85</v>
+      </c>
+      <c r="G69" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" t="s">
+        <v>82</v>
+      </c>
+      <c r="E70">
+        <v>48310</v>
+      </c>
+      <c r="F70" t="s">
+        <v>85</v>
+      </c>
+      <c r="G70" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" t="s">
+        <v>82</v>
+      </c>
+      <c r="E71">
+        <v>48310</v>
+      </c>
+      <c r="F71" t="s">
+        <v>85</v>
+      </c>
+      <c r="G71" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" t="s">
+        <v>50</v>
+      </c>
+      <c r="D72" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72">
+        <v>48460</v>
+      </c>
+      <c r="F72" t="s">
+        <v>85</v>
+      </c>
+      <c r="G72" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>7</v>
+      </c>
+      <c r="B73" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" t="s">
+        <v>50</v>
+      </c>
+      <c r="D73" t="s">
+        <v>82</v>
+      </c>
+      <c r="E73">
+        <v>48460</v>
+      </c>
+      <c r="F73" t="s">
+        <v>85</v>
+      </c>
+      <c r="G73" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" t="s">
+        <v>50</v>
+      </c>
+      <c r="D74" t="s">
+        <v>82</v>
+      </c>
+      <c r="E74">
+        <v>48460</v>
+      </c>
+      <c r="F74" t="s">
+        <v>85</v>
+      </c>
+      <c r="G74" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>7</v>
+      </c>
+      <c r="B75" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" t="s">
+        <v>83</v>
+      </c>
+      <c r="E75">
+        <v>49700</v>
+      </c>
+      <c r="F75" t="s">
+        <v>85</v>
+      </c>
+      <c r="G75" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>7</v>
+      </c>
+      <c r="B76" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" t="s">
+        <v>51</v>
+      </c>
+      <c r="D76" t="s">
+        <v>83</v>
+      </c>
+      <c r="E76">
+        <v>49700</v>
+      </c>
+      <c r="F76" t="s">
+        <v>85</v>
+      </c>
+      <c r="G76" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>7</v>
+      </c>
+      <c r="B77" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" t="s">
+        <v>51</v>
+      </c>
+      <c r="D77" t="s">
+        <v>83</v>
+      </c>
+      <c r="E77">
+        <v>49700</v>
+      </c>
+      <c r="F77" t="s">
+        <v>85</v>
+      </c>
+      <c r="G77" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>7</v>
+      </c>
+      <c r="B78" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" t="s">
+        <v>52</v>
+      </c>
+      <c r="D78" t="s">
+        <v>83</v>
+      </c>
+      <c r="E78">
+        <v>51090</v>
+      </c>
+      <c r="F78" t="s">
+        <v>85</v>
+      </c>
+      <c r="G78" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" t="s">
+        <v>52</v>
+      </c>
+      <c r="D79" t="s">
+        <v>83</v>
+      </c>
+      <c r="E79">
+        <v>51090</v>
+      </c>
+      <c r="F79" t="s">
+        <v>85</v>
+      </c>
+      <c r="G79" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" t="s">
+        <v>52</v>
+      </c>
+      <c r="D80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E80">
+        <v>51090</v>
+      </c>
+      <c r="F80" t="s">
+        <v>85</v>
+      </c>
+      <c r="G80" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>7</v>
+      </c>
+      <c r="B81" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" t="s">
+        <v>53</v>
+      </c>
+      <c r="D81" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81">
+        <v>52660</v>
+      </c>
+      <c r="F81" t="s">
+        <v>85</v>
+      </c>
+      <c r="G81" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" t="s">
+        <v>53</v>
+      </c>
+      <c r="D82" t="s">
+        <v>83</v>
+      </c>
+      <c r="E82">
+        <v>52660</v>
+      </c>
+      <c r="F82" t="s">
+        <v>85</v>
+      </c>
+      <c r="G82" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" t="s">
+        <v>53</v>
+      </c>
+      <c r="D83" t="s">
+        <v>83</v>
+      </c>
+      <c r="E83">
+        <v>52660</v>
+      </c>
+      <c r="F83" t="s">
+        <v>85</v>
+      </c>
+      <c r="G83" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" t="s">
+        <v>54</v>
+      </c>
+      <c r="D84" t="s">
+        <v>84</v>
+      </c>
+      <c r="E84">
         <v>54740</v>
       </c>
-      <c r="F13" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" t="s">
-        <v>41</v>
+      <c r="F84" t="s">
+        <v>85</v>
+      </c>
+      <c r="G84" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" t="s">
+        <v>54</v>
+      </c>
+      <c r="D85" t="s">
+        <v>84</v>
+      </c>
+      <c r="E85">
+        <v>54740</v>
+      </c>
+      <c r="F85" t="s">
+        <v>85</v>
+      </c>
+      <c r="G85" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
+        <v>54</v>
+      </c>
+      <c r="D86" t="s">
+        <v>84</v>
+      </c>
+      <c r="E86">
+        <v>54740</v>
+      </c>
+      <c r="F86" t="s">
+        <v>85</v>
+      </c>
+      <c r="G86" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/reports/BSH_Detayli_Fiyat_Raporu.xlsx
+++ b/reports/BSH_Detayli_Fiyat_Raporu.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="354">
   <si>
     <t>Marka</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Bosch</t>
   </si>
   <si>
+    <t>Siemens</t>
+  </si>
+  <si>
     <t>Bulaşık Makinesi</t>
   </si>
   <si>
@@ -181,6 +184,108 @@
     <t>WGK264ZRTR</t>
   </si>
   <si>
+    <t>SN15EC00NT</t>
+  </si>
+  <si>
+    <t>SN45EY01NT</t>
+  </si>
+  <si>
+    <t>SN45EB01NT</t>
+  </si>
+  <si>
+    <t>SN23HW62MT</t>
+  </si>
+  <si>
+    <t>SN23HY62MT</t>
+  </si>
+  <si>
+    <t>SN63HX62MT</t>
+  </si>
+  <si>
+    <t>SN25EI83CT</t>
+  </si>
+  <si>
+    <t>SN55ES82KT</t>
+  </si>
+  <si>
+    <t>SN75EX23CE</t>
+  </si>
+  <si>
+    <t>SN27YI82DT</t>
+  </si>
+  <si>
+    <t>SX95EX22CE</t>
+  </si>
+  <si>
+    <t>GU21NADE0</t>
+  </si>
+  <si>
+    <t>KU21RADE0</t>
+  </si>
+  <si>
+    <t>SN57ZS82DT</t>
+  </si>
+  <si>
+    <t>KI82LADD0</t>
+  </si>
+  <si>
+    <t>KB96NADD0</t>
+  </si>
+  <si>
+    <t>AS09XVW32N</t>
+  </si>
+  <si>
+    <t>AS12XVW32N</t>
+  </si>
+  <si>
+    <t>AS12XXB32N</t>
+  </si>
+  <si>
+    <t>AS18XVW32N</t>
+  </si>
+  <si>
+    <t>AS18XXB32N</t>
+  </si>
+  <si>
+    <t>AS24XVW32N</t>
+  </si>
+  <si>
+    <t>WG42K2ZXTR</t>
+  </si>
+  <si>
+    <t>WG44K2Z0TR</t>
+  </si>
+  <si>
+    <t>WG52K2Z0TR</t>
+  </si>
+  <si>
+    <t>WG52K2Z1TR</t>
+  </si>
+  <si>
+    <t>WG54K2Y0TR</t>
+  </si>
+  <si>
+    <t>WG52K2ZXTR</t>
+  </si>
+  <si>
+    <t>WG52K2ZSTR</t>
+  </si>
+  <si>
+    <t>WG64K2Z0TR</t>
+  </si>
+  <si>
+    <t>WG64K2Y0TR</t>
+  </si>
+  <si>
+    <t>WG64K2F0TR</t>
+  </si>
+  <si>
+    <t>WG64K2ZRTR</t>
+  </si>
+  <si>
+    <t>WG44B2A0TR</t>
+  </si>
+  <si>
     <t>Serie 6 Tam Ankastre Bulaşık Makinesi 60 cm</t>
   </si>
   <si>
@@ -271,6 +376,78 @@
     <t>Serie 6 Çamaşır Makinesi 11 kg maks. 1400 dev./dak., Antrasit</t>
   </si>
   <si>
+    <t>iQ500 Solo Bulaşık Makinesi 60 cm darkSteel Line</t>
+  </si>
+  <si>
+    <t>iQ500 Tezgah Altı Bulaşık Makinesi 60 cm</t>
+  </si>
+  <si>
+    <t>iQ500 Tezgah Altı Bulaşık Makinesi 60 cm Siyah</t>
+  </si>
+  <si>
+    <t>iQ500 Solo Bulaşık Makinesi 60 cm Beyaz</t>
+  </si>
+  <si>
+    <t>iQ500 Solo Bulaşık Makinesi 60 cm</t>
+  </si>
+  <si>
+    <t>iQ500 Tam Ankastre Bulaşık Makinesi 60 cm</t>
+  </si>
+  <si>
+    <t>iQ500 Solo Bulaşık Makinesi 60 cm Kolay Temizlenebilir Inox</t>
+  </si>
+  <si>
+    <t>iQ500 Yarı Ankastre Bulaşık Makinesi 60 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>iQ500 Tam Ankastre Bulaşık Makinesi 60 cm varioHinge</t>
+  </si>
+  <si>
+    <t>iQ700 Solo Bulaşık Makinesi 60 cm Kolay Temizlenebilir Inox</t>
+  </si>
+  <si>
+    <t>iQ500 Tam Ankastre Bulaşık Makinesi 60 cm , varioHinge</t>
+  </si>
+  <si>
+    <t>iQ500 Ankastre Derin Dondurucu 82 x 59.8 cm softClosing Düz Menteşe</t>
+  </si>
+  <si>
+    <t>iQ500 Tezgah Altı Ankastre Soğutucu 82 x 59.8 cm softClosing Düz Menteşe</t>
+  </si>
+  <si>
+    <t>iQ700 Yarı Ankastre Bulaşık Makinesi 60 cm Paslanmaz çelik</t>
+  </si>
+  <si>
+    <t>iQ500 Derin Donduruculu Ankastre Buzdolabı 177.2 x 55.8 cm softClosing Düz Menteşe</t>
+  </si>
+  <si>
+    <t>iQ500 Alttan Donduruculu Ankastre Buzdolabı 193.5 x 70.8 cm softClosing Düz Menteşe</t>
+  </si>
+  <si>
+    <t>iQ500 Çamaşır Makinesi 9 kg maks. 1200 dev./dak., Gümüş</t>
+  </si>
+  <si>
+    <t>iQ500 Çamaşır Makinesi 9 kg maks. 1400 dev./dak.</t>
+  </si>
+  <si>
+    <t>iQ500 Çamaşır Makinesi 10 kg maks. 1200 dev./dak.</t>
+  </si>
+  <si>
+    <t>iQ500 Çamaşır Makinesi 10 kg maks. 1400 dev./dak.</t>
+  </si>
+  <si>
+    <t>iQ500 Çamaşır Makinesi 10 kg maks. 1200 dev./dak., Gümüş</t>
+  </si>
+  <si>
+    <t>iQ500 Çamaşır Makinesi 11 kg maks. 1400 dev./dak.</t>
+  </si>
+  <si>
+    <t>iQ500 Çamaşır Makinesi 11 kg maks. 1400 dev./dak., Antrasit</t>
+  </si>
+  <si>
+    <t>iQ700 Çamaşır Makinesi 9 kg maks. 1400 dev./dak.</t>
+  </si>
+  <si>
     <t>Stokta Var</t>
   </si>
   <si>
@@ -280,18 +457,36 @@
     <t>2026-07-01 17:24:34</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:44</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:20</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:44</t>
   </si>
   <si>
     <t>2026-07-01 17:24:24</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:42</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:27</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:54</t>
   </si>
   <si>
     <t>2026-07-01 17:24:25</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:21</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:16</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:40</t>
   </si>
   <si>
@@ -310,114 +505,240 @@
     <t>2026-07-01 17:24:36</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:27</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:06:29</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:06:35</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:17</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:26</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:32</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:59</t>
   </si>
   <si>
     <t>2026-07-01 17:24:27</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:31</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:22</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:50</t>
   </si>
   <si>
     <t>2026-07-01 17:24:41</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:33</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:19</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:52</t>
   </si>
   <si>
     <t>2026-07-01 17:24:31</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:23</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:30</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:42</t>
   </si>
   <si>
     <t>2026-07-01 17:24:42</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:25</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:29</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:56</t>
   </si>
   <si>
     <t>2026-07-01 17:24:22</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:38</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:25</t>
+  </si>
+  <si>
     <t>2026-07-01 17:19:48</t>
   </si>
   <si>
     <t>2026-07-01 17:24:38</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:39</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:23</t>
+  </si>
+  <si>
     <t>2026-07-01 17:25:02</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:51</t>
+  </si>
+  <si>
     <t>2026-07-01 17:24:48</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:45</t>
+  </si>
+  <si>
     <t>2026-07-01 17:24:50</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:43</t>
+  </si>
+  <si>
     <t>2026-07-01 17:24:53</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:53</t>
+  </si>
+  <si>
     <t>2026-07-01 17:24:58</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:46</t>
+  </si>
+  <si>
     <t>2026-07-01 17:25:04</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:36</t>
+  </si>
+  <si>
     <t>2026-07-01 17:24:52</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:41</t>
+  </si>
+  <si>
     <t>2026-07-01 17:25:08</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:55</t>
+  </si>
+  <si>
     <t>2026-07-01 17:24:47</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:38</t>
+  </si>
+  <si>
     <t>2026-07-01 17:25:06</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:49</t>
+  </si>
+  <si>
     <t>2026-07-01 17:25:00</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:39</t>
+  </si>
+  <si>
     <t>2026-07-01 17:24:55</t>
   </si>
   <si>
+    <t>2026-07-01 18:13:48</t>
+  </si>
+  <si>
     <t>2026-07-01 17:20:11</t>
   </si>
   <si>
     <t>2026-07-01 17:25:19</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:53</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:00</t>
+  </si>
+  <si>
     <t>2026-07-01 17:20:13</t>
   </si>
   <si>
     <t>2026-07-01 17:25:13</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:54</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:06</t>
+  </si>
+  <si>
     <t>2026-07-01 17:20:16</t>
   </si>
   <si>
     <t>2026-07-01 17:25:21</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:56</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:59</t>
+  </si>
+  <si>
     <t>2026-07-01 17:20:17</t>
   </si>
   <si>
     <t>2026-07-01 17:25:12</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:59</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:01</t>
+  </si>
+  <si>
     <t>2026-07-01 17:20:08</t>
   </si>
   <si>
     <t>2026-07-01 17:25:17</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:51</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:03</t>
+  </si>
+  <si>
     <t>2026-07-01 17:20:10</t>
   </si>
   <si>
     <t>2026-07-01 17:25:15</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:58</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:04</t>
+  </si>
+  <si>
     <t>2026-07-01 17:16:14</t>
   </si>
   <si>
@@ -430,6 +751,12 @@
     <t>2026-07-01 17:24:12</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:17</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:12</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:50</t>
   </si>
   <si>
@@ -439,6 +766,12 @@
     <t>2026-07-01 17:24:11</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:13</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:04</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:59</t>
   </si>
   <si>
@@ -448,6 +781,12 @@
     <t>2026-07-01 17:24:09</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:11</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:03</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:46</t>
   </si>
   <si>
@@ -457,6 +796,12 @@
     <t>2026-07-01 17:24:04</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:15</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:12:56</t>
+  </si>
+  <si>
     <t>2026-07-01 16:56:02</t>
   </si>
   <si>
@@ -466,6 +811,12 @@
     <t>2026-07-01 17:24:00</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:02</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:07</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:49</t>
   </si>
   <si>
@@ -475,6 +826,12 @@
     <t>2026-07-01 17:24:16</t>
   </si>
   <si>
+    <t>2026-07-01 18:05:56</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:12:55</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:57</t>
   </si>
   <si>
@@ -484,6 +841,12 @@
     <t>2026-07-01 17:24:02</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:09</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:12:58</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:47</t>
   </si>
   <si>
@@ -493,6 +856,12 @@
     <t>2026-07-01 17:24:18</t>
   </si>
   <si>
+    <t>2026-07-01 18:05:58</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:06</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:55</t>
   </si>
   <si>
@@ -502,6 +871,12 @@
     <t>2026-07-01 17:24:06</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:03</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:02</t>
+  </si>
+  <si>
     <t>2026-07-01 16:56:00</t>
   </si>
   <si>
@@ -511,6 +886,12 @@
     <t>2026-07-01 17:23:58</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:00</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:12:59</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:53</t>
   </si>
   <si>
@@ -520,6 +901,12 @@
     <t>2026-07-01 17:24:14</t>
   </si>
   <si>
+    <t>2026-07-01 18:06:05</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:10</t>
+  </si>
+  <si>
     <t>2026-07-01 16:55:52</t>
   </si>
   <si>
@@ -527,6 +914,168 @@
   </si>
   <si>
     <t>2026-07-01 17:24:07</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:06:07</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:13:09</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:50</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:44</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:46</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:38</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:42</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:40</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:36</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:30</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:32</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:34</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:52</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:32</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:31</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:48</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:37</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:36</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:59</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:48</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:08:07</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:51</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:08:03</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:53</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:08:01</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:44</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:08:05</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:49</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:08:08</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:46</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:12</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:25</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:22</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:26</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:06</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:23</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:08</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:20</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:14</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:15</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:10</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:18</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:16</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:17</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:04</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:13</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:20</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:14</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:23</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:22</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:25</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:11</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:07:18</t>
+  </si>
+  <si>
+    <t>2026-07-01 18:14:10</t>
   </si>
 </sst>
 </file>
@@ -884,7 +1433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -915,22 +1464,22 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E2">
         <v>44350</v>
       </c>
       <c r="F2" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -938,22 +1487,22 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="E3">
         <v>44350</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -961,22 +1510,22 @@
         <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="E4">
-        <v>44430</v>
+        <v>44350</v>
       </c>
       <c r="F4" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -984,22 +1533,22 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
         <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="E5">
-        <v>44430</v>
+        <v>44350</v>
       </c>
       <c r="F5" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1007,22 +1556,22 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E6">
-        <v>45080</v>
+        <v>44430</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1030,22 +1579,22 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="E7">
-        <v>45080</v>
+        <v>44430</v>
       </c>
       <c r="F7" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1053,22 +1602,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="E8">
-        <v>47010</v>
+        <v>44430</v>
       </c>
       <c r="F8" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1076,22 +1625,22 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="E9">
-        <v>47010</v>
+        <v>44430</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>152</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1099,22 +1648,22 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D10" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E10">
-        <v>47010</v>
+        <v>45080</v>
       </c>
       <c r="F10" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G10" t="s">
-        <v>94</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1122,22 +1671,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
         <v>15</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="E11">
-        <v>47010</v>
+        <v>45080</v>
       </c>
       <c r="F11" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G11" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1145,22 +1694,22 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="E12">
-        <v>47010</v>
+        <v>45080</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G12" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1168,22 +1717,22 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E13">
-        <v>47010</v>
+        <v>45080</v>
       </c>
       <c r="F13" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G13" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1191,22 +1740,22 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="E14">
-        <v>51300</v>
+        <v>47010</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G14" t="s">
-        <v>98</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1214,22 +1763,22 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" t="s">
-        <v>59</v>
+        <v>94</v>
       </c>
       <c r="E15">
-        <v>51300</v>
+        <v>47010</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G15" t="s">
-        <v>99</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1237,22 +1786,22 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="E16">
-        <v>59970</v>
+        <v>47010</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G16" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1260,22 +1809,22 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D17" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="E17">
-        <v>59970</v>
+        <v>47010</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1283,22 +1832,22 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="E18">
-        <v>62580</v>
+        <v>47010</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1306,22 +1855,22 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>95</v>
       </c>
       <c r="E19">
-        <v>62580</v>
+        <v>47010</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1329,22 +1878,22 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="E20">
-        <v>63200</v>
+        <v>47010</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G20" t="s">
-        <v>104</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1352,22 +1901,22 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="E21">
-        <v>63200</v>
+        <v>47010</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G21" t="s">
-        <v>105</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1375,22 +1924,22 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E22">
-        <v>66470</v>
+        <v>47010</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G22" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1398,22 +1947,22 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="E23">
-        <v>66470</v>
+        <v>47010</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G23" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1421,22 +1970,22 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="E24">
-        <v>81510</v>
+        <v>47010</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G24" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1444,22 +1993,22 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="E25">
-        <v>81510</v>
+        <v>47010</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G25" t="s">
-        <v>109</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1470,19 +2019,19 @@
         <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>94</v>
       </c>
       <c r="E26">
-        <v>87390</v>
+        <v>51300</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G26" t="s">
-        <v>110</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1493,19 +2042,19 @@
         <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="E27">
-        <v>87890</v>
+        <v>51300</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G27" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1516,19 +2065,19 @@
         <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D28" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="E28">
-        <v>88600</v>
+        <v>51300</v>
       </c>
       <c r="F28" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G28" t="s">
-        <v>112</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1539,19 +2088,19 @@
         <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D29" t="s">
-        <v>67</v>
+        <v>94</v>
       </c>
       <c r="E29">
-        <v>94490</v>
+        <v>51300</v>
       </c>
       <c r="F29" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G29" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1562,19 +2111,19 @@
         <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D30" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E30">
-        <v>94890</v>
+        <v>59970</v>
       </c>
       <c r="F30" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1585,19 +2134,19 @@
         <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="E31">
-        <v>95390</v>
+        <v>59970</v>
       </c>
       <c r="F31" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G31" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1608,19 +2157,19 @@
         <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="E32">
-        <v>96750</v>
+        <v>59970</v>
       </c>
       <c r="F32" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G32" t="s">
-        <v>116</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1631,19 +2180,19 @@
         <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="E33">
-        <v>99790</v>
+        <v>59970</v>
       </c>
       <c r="F33" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G33" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1654,19 +2203,19 @@
         <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>96</v>
       </c>
       <c r="E34">
-        <v>105790</v>
+        <v>62580</v>
       </c>
       <c r="F34" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1677,19 +2226,19 @@
         <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D35" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E35">
-        <v>115290</v>
+        <v>62580</v>
       </c>
       <c r="F35" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G35" t="s">
-        <v>119</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1700,19 +2249,19 @@
         <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D36" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="E36">
-        <v>122990</v>
+        <v>62580</v>
       </c>
       <c r="F36" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G36" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1723,19 +2272,19 @@
         <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D37" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="E37">
-        <v>127110</v>
+        <v>62580</v>
       </c>
       <c r="F37" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G37" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1743,22 +2292,22 @@
         <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E38">
-        <v>45700</v>
+        <v>63200</v>
       </c>
       <c r="F38" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G38" t="s">
-        <v>122</v>
+        <v>181</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1766,22 +2315,22 @@
         <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D39" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E39">
-        <v>45700</v>
+        <v>63200</v>
       </c>
       <c r="F39" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G39" t="s">
-        <v>123</v>
+        <v>182</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1789,22 +2338,22 @@
         <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D40" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E40">
-        <v>50200</v>
+        <v>63200</v>
       </c>
       <c r="F40" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G40" t="s">
-        <v>124</v>
+        <v>183</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1812,22 +2361,22 @@
         <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C41" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D41" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E41">
-        <v>50200</v>
+        <v>63200</v>
       </c>
       <c r="F41" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G41" t="s">
-        <v>125</v>
+        <v>184</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1835,22 +2384,22 @@
         <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C42" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="E42">
-        <v>56030</v>
+        <v>66470</v>
       </c>
       <c r="F42" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G42" t="s">
-        <v>126</v>
+        <v>185</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1858,22 +2407,22 @@
         <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C43" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D43" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="E43">
-        <v>56030</v>
+        <v>66470</v>
       </c>
       <c r="F43" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G43" t="s">
-        <v>127</v>
+        <v>186</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1881,22 +2430,22 @@
         <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D44" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="E44">
-        <v>70810</v>
+        <v>66470</v>
       </c>
       <c r="F44" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G44" t="s">
-        <v>128</v>
+        <v>187</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1904,22 +2453,22 @@
         <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="E45">
-        <v>70810</v>
+        <v>66470</v>
       </c>
       <c r="F45" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G45" t="s">
-        <v>129</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1927,22 +2476,22 @@
         <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C46" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D46" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E46">
-        <v>79070</v>
+        <v>81510</v>
       </c>
       <c r="F46" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G46" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1950,22 +2499,22 @@
         <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C47" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E47">
-        <v>79070</v>
+        <v>81510</v>
       </c>
       <c r="F47" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G47" t="s">
-        <v>131</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1973,22 +2522,22 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C48" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E48">
-        <v>85790</v>
+        <v>81510</v>
       </c>
       <c r="F48" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G48" t="s">
-        <v>132</v>
+        <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1996,22 +2545,22 @@
         <v>7</v>
       </c>
       <c r="B49" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C49" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="E49">
-        <v>85790</v>
+        <v>81510</v>
       </c>
       <c r="F49" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G49" t="s">
-        <v>133</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2019,22 +2568,22 @@
         <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C50" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="E50">
-        <v>24500</v>
+        <v>87390</v>
       </c>
       <c r="F50" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G50" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2042,22 +2591,22 @@
         <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C51" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="D51" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="E51">
-        <v>44510</v>
+        <v>87390</v>
       </c>
       <c r="F51" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G51" t="s">
-        <v>135</v>
+        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2065,22 +2614,22 @@
         <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C52" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E52">
-        <v>44510</v>
+        <v>87890</v>
       </c>
       <c r="F52" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G52" t="s">
-        <v>136</v>
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2088,22 +2637,22 @@
         <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E53">
-        <v>44510</v>
+        <v>87890</v>
       </c>
       <c r="F53" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G53" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2111,22 +2660,22 @@
         <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D54" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E54">
-        <v>46040</v>
+        <v>88600</v>
       </c>
       <c r="F54" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G54" t="s">
-        <v>138</v>
+        <v>197</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2134,22 +2683,22 @@
         <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D55" t="s">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="E55">
-        <v>46040</v>
+        <v>88600</v>
       </c>
       <c r="F55" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G55" t="s">
-        <v>139</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2157,22 +2706,22 @@
         <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D56" t="s">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="E56">
-        <v>46040</v>
+        <v>94490</v>
       </c>
       <c r="F56" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G56" t="s">
-        <v>140</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2180,22 +2729,22 @@
         <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C57" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="E57">
-        <v>46210</v>
+        <v>94490</v>
       </c>
       <c r="F57" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G57" t="s">
-        <v>141</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2203,22 +2752,22 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C58" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D58" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="E58">
-        <v>46210</v>
+        <v>94890</v>
       </c>
       <c r="F58" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G58" t="s">
-        <v>142</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2226,22 +2775,22 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C59" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="D59" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="E59">
-        <v>46210</v>
+        <v>94890</v>
       </c>
       <c r="F59" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G59" t="s">
-        <v>143</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2249,22 +2798,22 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C60" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D60" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E60">
-        <v>46440</v>
+        <v>95390</v>
       </c>
       <c r="F60" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G60" t="s">
-        <v>144</v>
+        <v>203</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2272,22 +2821,22 @@
         <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C61" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="D61" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="E61">
-        <v>46440</v>
+        <v>95390</v>
       </c>
       <c r="F61" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G61" t="s">
-        <v>145</v>
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2295,22 +2844,22 @@
         <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C62" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E62">
-        <v>46440</v>
+        <v>96750</v>
       </c>
       <c r="F62" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G62" t="s">
-        <v>146</v>
+        <v>205</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2318,22 +2867,22 @@
         <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D63" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="E63">
-        <v>46560</v>
+        <v>96750</v>
       </c>
       <c r="F63" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G63" t="s">
-        <v>147</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2341,22 +2890,22 @@
         <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D64" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E64">
-        <v>46560</v>
+        <v>99790</v>
       </c>
       <c r="F64" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G64" t="s">
-        <v>148</v>
+        <v>207</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2364,22 +2913,22 @@
         <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="E65">
-        <v>46560</v>
+        <v>99790</v>
       </c>
       <c r="F65" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G65" t="s">
-        <v>149</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -2387,22 +2936,22 @@
         <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D66" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="E66">
-        <v>47150</v>
+        <v>105790</v>
       </c>
       <c r="F66" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G66" t="s">
-        <v>150</v>
+        <v>209</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -2410,22 +2959,22 @@
         <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C67" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D67" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="E67">
-        <v>47150</v>
+        <v>105790</v>
       </c>
       <c r="F67" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G67" t="s">
-        <v>151</v>
+        <v>210</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -2433,22 +2982,22 @@
         <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C68" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="E68">
-        <v>47150</v>
+        <v>115290</v>
       </c>
       <c r="F68" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G68" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -2456,22 +3005,22 @@
         <v>7</v>
       </c>
       <c r="B69" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D69" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="E69">
-        <v>48310</v>
+        <v>115290</v>
       </c>
       <c r="F69" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G69" t="s">
-        <v>153</v>
+        <v>212</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -2479,22 +3028,22 @@
         <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C70" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D70" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="E70">
-        <v>48310</v>
+        <v>122990</v>
       </c>
       <c r="F70" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G70" t="s">
-        <v>154</v>
+        <v>213</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2502,22 +3051,22 @@
         <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D71" t="s">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="E71">
-        <v>48310</v>
+        <v>122990</v>
       </c>
       <c r="F71" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G71" t="s">
-        <v>155</v>
+        <v>214</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2525,22 +3074,22 @@
         <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C72" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D72" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="E72">
-        <v>48460</v>
+        <v>127110</v>
       </c>
       <c r="F72" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G72" t="s">
-        <v>156</v>
+        <v>215</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2548,22 +3097,22 @@
         <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C73" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="D73" t="s">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="E73">
-        <v>48460</v>
+        <v>127110</v>
       </c>
       <c r="F73" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G73" t="s">
-        <v>157</v>
+        <v>216</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2574,19 +3123,19 @@
         <v>11</v>
       </c>
       <c r="C74" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="D74" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E74">
-        <v>48460</v>
+        <v>45700</v>
       </c>
       <c r="F74" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G74" t="s">
-        <v>158</v>
+        <v>217</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2597,19 +3146,19 @@
         <v>11</v>
       </c>
       <c r="C75" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D75" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E75">
-        <v>49700</v>
+        <v>45700</v>
       </c>
       <c r="F75" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G75" t="s">
-        <v>159</v>
+        <v>218</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2620,19 +3169,19 @@
         <v>11</v>
       </c>
       <c r="C76" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D76" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E76">
-        <v>49700</v>
+        <v>45700</v>
       </c>
       <c r="F76" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G76" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2643,19 +3192,19 @@
         <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D77" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E77">
-        <v>49700</v>
+        <v>45700</v>
       </c>
       <c r="F77" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G77" t="s">
-        <v>161</v>
+        <v>220</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2666,19 +3215,19 @@
         <v>11</v>
       </c>
       <c r="C78" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D78" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E78">
-        <v>51090</v>
+        <v>50200</v>
       </c>
       <c r="F78" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G78" t="s">
-        <v>162</v>
+        <v>221</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2689,19 +3238,19 @@
         <v>11</v>
       </c>
       <c r="C79" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E79">
-        <v>51090</v>
+        <v>50200</v>
       </c>
       <c r="F79" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G79" t="s">
-        <v>163</v>
+        <v>222</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2712,19 +3261,19 @@
         <v>11</v>
       </c>
       <c r="C80" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="D80" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E80">
-        <v>51090</v>
+        <v>50200</v>
       </c>
       <c r="F80" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G80" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2735,19 +3284,19 @@
         <v>11</v>
       </c>
       <c r="C81" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D81" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E81">
-        <v>52660</v>
+        <v>50200</v>
       </c>
       <c r="F81" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G81" t="s">
-        <v>165</v>
+        <v>224</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2758,19 +3307,19 @@
         <v>11</v>
       </c>
       <c r="C82" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D82" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E82">
-        <v>52660</v>
+        <v>56030</v>
       </c>
       <c r="F82" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G82" t="s">
-        <v>166</v>
+        <v>225</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2781,19 +3330,19 @@
         <v>11</v>
       </c>
       <c r="C83" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D83" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="E83">
-        <v>52660</v>
+        <v>56030</v>
       </c>
       <c r="F83" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G83" t="s">
-        <v>167</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2804,19 +3353,19 @@
         <v>11</v>
       </c>
       <c r="C84" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D84" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="E84">
-        <v>54740</v>
+        <v>56030</v>
       </c>
       <c r="F84" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G84" t="s">
-        <v>168</v>
+        <v>227</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2827,19 +3376,19 @@
         <v>11</v>
       </c>
       <c r="C85" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D85" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="E85">
-        <v>54740</v>
+        <v>56030</v>
       </c>
       <c r="F85" t="s">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="G85" t="s">
-        <v>169</v>
+        <v>228</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2850,19 +3399,2871 @@
         <v>11</v>
       </c>
       <c r="C86" t="s">
+        <v>40</v>
+      </c>
+      <c r="D86" t="s">
+        <v>110</v>
+      </c>
+      <c r="E86">
+        <v>70810</v>
+      </c>
+      <c r="F86" t="s">
+        <v>144</v>
+      </c>
+      <c r="G86" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" t="s">
+        <v>40</v>
+      </c>
+      <c r="D87" t="s">
+        <v>110</v>
+      </c>
+      <c r="E87">
+        <v>70810</v>
+      </c>
+      <c r="F87" t="s">
+        <v>144</v>
+      </c>
+      <c r="G87" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>40</v>
+      </c>
+      <c r="D88" t="s">
+        <v>110</v>
+      </c>
+      <c r="E88">
+        <v>70810</v>
+      </c>
+      <c r="F88" t="s">
+        <v>144</v>
+      </c>
+      <c r="G88" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>40</v>
+      </c>
+      <c r="D89" t="s">
+        <v>110</v>
+      </c>
+      <c r="E89">
+        <v>70810</v>
+      </c>
+      <c r="F89" t="s">
+        <v>144</v>
+      </c>
+      <c r="G89" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" t="s">
+        <v>41</v>
+      </c>
+      <c r="D90" t="s">
+        <v>110</v>
+      </c>
+      <c r="E90">
+        <v>79070</v>
+      </c>
+      <c r="F90" t="s">
+        <v>144</v>
+      </c>
+      <c r="G90" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>7</v>
+      </c>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>41</v>
+      </c>
+      <c r="D91" t="s">
+        <v>110</v>
+      </c>
+      <c r="E91">
+        <v>79070</v>
+      </c>
+      <c r="F91" t="s">
+        <v>144</v>
+      </c>
+      <c r="G91" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>7</v>
+      </c>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" t="s">
+        <v>41</v>
+      </c>
+      <c r="D92" t="s">
+        <v>110</v>
+      </c>
+      <c r="E92">
+        <v>79070</v>
+      </c>
+      <c r="F92" t="s">
+        <v>144</v>
+      </c>
+      <c r="G92" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>7</v>
+      </c>
+      <c r="B93" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" t="s">
+        <v>41</v>
+      </c>
+      <c r="D93" t="s">
+        <v>110</v>
+      </c>
+      <c r="E93">
+        <v>79070</v>
+      </c>
+      <c r="F93" t="s">
+        <v>144</v>
+      </c>
+      <c r="G93" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>7</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
+        <v>42</v>
+      </c>
+      <c r="D94" t="s">
+        <v>110</v>
+      </c>
+      <c r="E94">
+        <v>85790</v>
+      </c>
+      <c r="F94" t="s">
+        <v>144</v>
+      </c>
+      <c r="G94" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>7</v>
+      </c>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" t="s">
+        <v>42</v>
+      </c>
+      <c r="D95" t="s">
+        <v>110</v>
+      </c>
+      <c r="E95">
+        <v>85790</v>
+      </c>
+      <c r="F95" t="s">
+        <v>144</v>
+      </c>
+      <c r="G95" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" t="s">
+        <v>42</v>
+      </c>
+      <c r="D96" t="s">
+        <v>110</v>
+      </c>
+      <c r="E96">
+        <v>85790</v>
+      </c>
+      <c r="F96" t="s">
+        <v>144</v>
+      </c>
+      <c r="G96" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>7</v>
+      </c>
+      <c r="B97" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" t="s">
+        <v>42</v>
+      </c>
+      <c r="D97" t="s">
+        <v>110</v>
+      </c>
+      <c r="E97">
+        <v>85790</v>
+      </c>
+      <c r="F97" t="s">
+        <v>144</v>
+      </c>
+      <c r="G97" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>7</v>
+      </c>
+      <c r="B98" t="s">
+        <v>12</v>
+      </c>
+      <c r="C98" t="s">
+        <v>43</v>
+      </c>
+      <c r="D98" t="s">
+        <v>111</v>
+      </c>
+      <c r="E98">
+        <v>24500</v>
+      </c>
+      <c r="F98" t="s">
+        <v>144</v>
+      </c>
+      <c r="G98" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>7</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>44</v>
+      </c>
+      <c r="D99" t="s">
+        <v>112</v>
+      </c>
+      <c r="E99">
+        <v>44510</v>
+      </c>
+      <c r="F99" t="s">
+        <v>144</v>
+      </c>
+      <c r="G99" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>7</v>
+      </c>
+      <c r="B100" t="s">
+        <v>12</v>
+      </c>
+      <c r="C100" t="s">
+        <v>44</v>
+      </c>
+      <c r="D100" t="s">
+        <v>112</v>
+      </c>
+      <c r="E100">
+        <v>44510</v>
+      </c>
+      <c r="F100" t="s">
+        <v>144</v>
+      </c>
+      <c r="G100" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>7</v>
+      </c>
+      <c r="B101" t="s">
+        <v>12</v>
+      </c>
+      <c r="C101" t="s">
+        <v>44</v>
+      </c>
+      <c r="D101" t="s">
+        <v>112</v>
+      </c>
+      <c r="E101">
+        <v>44510</v>
+      </c>
+      <c r="F101" t="s">
+        <v>144</v>
+      </c>
+      <c r="G101" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>7</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>44</v>
+      </c>
+      <c r="D102" t="s">
+        <v>112</v>
+      </c>
+      <c r="E102">
+        <v>44510</v>
+      </c>
+      <c r="F102" t="s">
+        <v>144</v>
+      </c>
+      <c r="G102" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>7</v>
+      </c>
+      <c r="B103" t="s">
+        <v>12</v>
+      </c>
+      <c r="C103" t="s">
+        <v>44</v>
+      </c>
+      <c r="D103" t="s">
+        <v>112</v>
+      </c>
+      <c r="E103">
+        <v>44510</v>
+      </c>
+      <c r="F103" t="s">
+        <v>144</v>
+      </c>
+      <c r="G103" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>7</v>
+      </c>
+      <c r="B104" t="s">
+        <v>12</v>
+      </c>
+      <c r="C104" t="s">
+        <v>45</v>
+      </c>
+      <c r="D104" t="s">
+        <v>113</v>
+      </c>
+      <c r="E104">
+        <v>46040</v>
+      </c>
+      <c r="F104" t="s">
+        <v>144</v>
+      </c>
+      <c r="G104" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>7</v>
+      </c>
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" t="s">
+        <v>45</v>
+      </c>
+      <c r="D105" t="s">
+        <v>113</v>
+      </c>
+      <c r="E105">
+        <v>46040</v>
+      </c>
+      <c r="F105" t="s">
+        <v>144</v>
+      </c>
+      <c r="G105" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>7</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106" t="s">
+        <v>45</v>
+      </c>
+      <c r="D106" t="s">
+        <v>113</v>
+      </c>
+      <c r="E106">
+        <v>46040</v>
+      </c>
+      <c r="F106" t="s">
+        <v>144</v>
+      </c>
+      <c r="G106" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>7</v>
+      </c>
+      <c r="B107" t="s">
+        <v>12</v>
+      </c>
+      <c r="C107" t="s">
+        <v>45</v>
+      </c>
+      <c r="D107" t="s">
+        <v>113</v>
+      </c>
+      <c r="E107">
+        <v>46040</v>
+      </c>
+      <c r="F107" t="s">
+        <v>144</v>
+      </c>
+      <c r="G107" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>7</v>
+      </c>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" t="s">
+        <v>45</v>
+      </c>
+      <c r="D108" t="s">
+        <v>113</v>
+      </c>
+      <c r="E108">
+        <v>46040</v>
+      </c>
+      <c r="F108" t="s">
+        <v>144</v>
+      </c>
+      <c r="G108" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>7</v>
+      </c>
+      <c r="B109" t="s">
+        <v>12</v>
+      </c>
+      <c r="C109" t="s">
+        <v>46</v>
+      </c>
+      <c r="D109" t="s">
+        <v>114</v>
+      </c>
+      <c r="E109">
+        <v>46210</v>
+      </c>
+      <c r="F109" t="s">
+        <v>144</v>
+      </c>
+      <c r="G109" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>7</v>
+      </c>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" t="s">
+        <v>46</v>
+      </c>
+      <c r="D110" t="s">
+        <v>114</v>
+      </c>
+      <c r="E110">
+        <v>46210</v>
+      </c>
+      <c r="F110" t="s">
+        <v>144</v>
+      </c>
+      <c r="G110" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7">
+      <c r="A111" t="s">
+        <v>7</v>
+      </c>
+      <c r="B111" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" t="s">
+        <v>46</v>
+      </c>
+      <c r="D111" t="s">
+        <v>114</v>
+      </c>
+      <c r="E111">
+        <v>46210</v>
+      </c>
+      <c r="F111" t="s">
+        <v>144</v>
+      </c>
+      <c r="G111" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7">
+      <c r="A112" t="s">
+        <v>7</v>
+      </c>
+      <c r="B112" t="s">
+        <v>12</v>
+      </c>
+      <c r="C112" t="s">
+        <v>46</v>
+      </c>
+      <c r="D112" t="s">
+        <v>114</v>
+      </c>
+      <c r="E112">
+        <v>46210</v>
+      </c>
+      <c r="F112" t="s">
+        <v>144</v>
+      </c>
+      <c r="G112" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7">
+      <c r="A113" t="s">
+        <v>7</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" t="s">
+        <v>46</v>
+      </c>
+      <c r="D113" t="s">
+        <v>114</v>
+      </c>
+      <c r="E113">
+        <v>46210</v>
+      </c>
+      <c r="F113" t="s">
+        <v>144</v>
+      </c>
+      <c r="G113" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7">
+      <c r="A114" t="s">
+        <v>7</v>
+      </c>
+      <c r="B114" t="s">
+        <v>12</v>
+      </c>
+      <c r="C114" t="s">
+        <v>47</v>
+      </c>
+      <c r="D114" t="s">
+        <v>115</v>
+      </c>
+      <c r="E114">
+        <v>46440</v>
+      </c>
+      <c r="F114" t="s">
+        <v>144</v>
+      </c>
+      <c r="G114" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7">
+      <c r="A115" t="s">
+        <v>7</v>
+      </c>
+      <c r="B115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115" t="s">
+        <v>47</v>
+      </c>
+      <c r="D115" t="s">
+        <v>115</v>
+      </c>
+      <c r="E115">
+        <v>46440</v>
+      </c>
+      <c r="F115" t="s">
+        <v>144</v>
+      </c>
+      <c r="G115" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7">
+      <c r="A116" t="s">
+        <v>7</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" t="s">
+        <v>47</v>
+      </c>
+      <c r="D116" t="s">
+        <v>115</v>
+      </c>
+      <c r="E116">
+        <v>46440</v>
+      </c>
+      <c r="F116" t="s">
+        <v>144</v>
+      </c>
+      <c r="G116" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7">
+      <c r="A117" t="s">
+        <v>7</v>
+      </c>
+      <c r="B117" t="s">
+        <v>12</v>
+      </c>
+      <c r="C117" t="s">
+        <v>47</v>
+      </c>
+      <c r="D117" t="s">
+        <v>115</v>
+      </c>
+      <c r="E117">
+        <v>46440</v>
+      </c>
+      <c r="F117" t="s">
+        <v>144</v>
+      </c>
+      <c r="G117" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7">
+      <c r="A118" t="s">
+        <v>7</v>
+      </c>
+      <c r="B118" t="s">
+        <v>12</v>
+      </c>
+      <c r="C118" t="s">
+        <v>47</v>
+      </c>
+      <c r="D118" t="s">
+        <v>115</v>
+      </c>
+      <c r="E118">
+        <v>46440</v>
+      </c>
+      <c r="F118" t="s">
+        <v>144</v>
+      </c>
+      <c r="G118" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7">
+      <c r="A119" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>48</v>
+      </c>
+      <c r="D119" t="s">
+        <v>115</v>
+      </c>
+      <c r="E119">
+        <v>46560</v>
+      </c>
+      <c r="F119" t="s">
+        <v>144</v>
+      </c>
+      <c r="G119" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7">
+      <c r="A120" t="s">
+        <v>7</v>
+      </c>
+      <c r="B120" t="s">
+        <v>12</v>
+      </c>
+      <c r="C120" t="s">
+        <v>48</v>
+      </c>
+      <c r="D120" t="s">
+        <v>115</v>
+      </c>
+      <c r="E120">
+        <v>46560</v>
+      </c>
+      <c r="F120" t="s">
+        <v>144</v>
+      </c>
+      <c r="G120" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7">
+      <c r="A121" t="s">
+        <v>7</v>
+      </c>
+      <c r="B121" t="s">
+        <v>12</v>
+      </c>
+      <c r="C121" t="s">
+        <v>48</v>
+      </c>
+      <c r="D121" t="s">
+        <v>115</v>
+      </c>
+      <c r="E121">
+        <v>46560</v>
+      </c>
+      <c r="F121" t="s">
+        <v>144</v>
+      </c>
+      <c r="G121" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7">
+      <c r="A122" t="s">
+        <v>7</v>
+      </c>
+      <c r="B122" t="s">
+        <v>12</v>
+      </c>
+      <c r="C122" t="s">
+        <v>48</v>
+      </c>
+      <c r="D122" t="s">
+        <v>115</v>
+      </c>
+      <c r="E122">
+        <v>46560</v>
+      </c>
+      <c r="F122" t="s">
+        <v>144</v>
+      </c>
+      <c r="G122" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7">
+      <c r="A123" t="s">
+        <v>7</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123" t="s">
+        <v>48</v>
+      </c>
+      <c r="D123" t="s">
+        <v>115</v>
+      </c>
+      <c r="E123">
+        <v>46560</v>
+      </c>
+      <c r="F123" t="s">
+        <v>144</v>
+      </c>
+      <c r="G123" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7">
+      <c r="A124" t="s">
+        <v>7</v>
+      </c>
+      <c r="B124" t="s">
+        <v>12</v>
+      </c>
+      <c r="C124" t="s">
+        <v>49</v>
+      </c>
+      <c r="D124" t="s">
+        <v>116</v>
+      </c>
+      <c r="E124">
+        <v>47150</v>
+      </c>
+      <c r="F124" t="s">
+        <v>144</v>
+      </c>
+      <c r="G124" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7">
+      <c r="A125" t="s">
+        <v>7</v>
+      </c>
+      <c r="B125" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" t="s">
+        <v>49</v>
+      </c>
+      <c r="D125" t="s">
+        <v>116</v>
+      </c>
+      <c r="E125">
+        <v>47150</v>
+      </c>
+      <c r="F125" t="s">
+        <v>144</v>
+      </c>
+      <c r="G125" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7">
+      <c r="A126" t="s">
+        <v>7</v>
+      </c>
+      <c r="B126" t="s">
+        <v>12</v>
+      </c>
+      <c r="C126" t="s">
+        <v>49</v>
+      </c>
+      <c r="D126" t="s">
+        <v>116</v>
+      </c>
+      <c r="E126">
+        <v>47150</v>
+      </c>
+      <c r="F126" t="s">
+        <v>144</v>
+      </c>
+      <c r="G126" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7">
+      <c r="A127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B127" t="s">
+        <v>12</v>
+      </c>
+      <c r="C127" t="s">
+        <v>49</v>
+      </c>
+      <c r="D127" t="s">
+        <v>116</v>
+      </c>
+      <c r="E127">
+        <v>47150</v>
+      </c>
+      <c r="F127" t="s">
+        <v>144</v>
+      </c>
+      <c r="G127" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7">
+      <c r="A128" t="s">
+        <v>7</v>
+      </c>
+      <c r="B128" t="s">
+        <v>12</v>
+      </c>
+      <c r="C128" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" t="s">
+        <v>116</v>
+      </c>
+      <c r="E128">
+        <v>47150</v>
+      </c>
+      <c r="F128" t="s">
+        <v>144</v>
+      </c>
+      <c r="G128" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7">
+      <c r="A129" t="s">
+        <v>7</v>
+      </c>
+      <c r="B129" t="s">
+        <v>12</v>
+      </c>
+      <c r="C129" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" t="s">
+        <v>117</v>
+      </c>
+      <c r="E129">
+        <v>48310</v>
+      </c>
+      <c r="F129" t="s">
+        <v>144</v>
+      </c>
+      <c r="G129" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7">
+      <c r="A130" t="s">
+        <v>7</v>
+      </c>
+      <c r="B130" t="s">
+        <v>12</v>
+      </c>
+      <c r="C130" t="s">
+        <v>50</v>
+      </c>
+      <c r="D130" t="s">
+        <v>117</v>
+      </c>
+      <c r="E130">
+        <v>48310</v>
+      </c>
+      <c r="F130" t="s">
+        <v>144</v>
+      </c>
+      <c r="G130" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7">
+      <c r="A131" t="s">
+        <v>7</v>
+      </c>
+      <c r="B131" t="s">
+        <v>12</v>
+      </c>
+      <c r="C131" t="s">
+        <v>50</v>
+      </c>
+      <c r="D131" t="s">
+        <v>117</v>
+      </c>
+      <c r="E131">
+        <v>48310</v>
+      </c>
+      <c r="F131" t="s">
+        <v>144</v>
+      </c>
+      <c r="G131" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7">
+      <c r="A132" t="s">
+        <v>7</v>
+      </c>
+      <c r="B132" t="s">
+        <v>12</v>
+      </c>
+      <c r="C132" t="s">
+        <v>50</v>
+      </c>
+      <c r="D132" t="s">
+        <v>117</v>
+      </c>
+      <c r="E132">
+        <v>48310</v>
+      </c>
+      <c r="F132" t="s">
+        <v>144</v>
+      </c>
+      <c r="G132" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7">
+      <c r="A133" t="s">
+        <v>7</v>
+      </c>
+      <c r="B133" t="s">
+        <v>12</v>
+      </c>
+      <c r="C133" t="s">
+        <v>50</v>
+      </c>
+      <c r="D133" t="s">
+        <v>117</v>
+      </c>
+      <c r="E133">
+        <v>48310</v>
+      </c>
+      <c r="F133" t="s">
+        <v>144</v>
+      </c>
+      <c r="G133" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7">
+      <c r="A134" t="s">
+        <v>7</v>
+      </c>
+      <c r="B134" t="s">
+        <v>12</v>
+      </c>
+      <c r="C134" t="s">
+        <v>51</v>
+      </c>
+      <c r="D134" t="s">
+        <v>117</v>
+      </c>
+      <c r="E134">
+        <v>48460</v>
+      </c>
+      <c r="F134" t="s">
+        <v>144</v>
+      </c>
+      <c r="G134" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7">
+      <c r="A135" t="s">
+        <v>7</v>
+      </c>
+      <c r="B135" t="s">
+        <v>12</v>
+      </c>
+      <c r="C135" t="s">
+        <v>51</v>
+      </c>
+      <c r="D135" t="s">
+        <v>117</v>
+      </c>
+      <c r="E135">
+        <v>48460</v>
+      </c>
+      <c r="F135" t="s">
+        <v>144</v>
+      </c>
+      <c r="G135" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7">
+      <c r="A136" t="s">
+        <v>7</v>
+      </c>
+      <c r="B136" t="s">
+        <v>12</v>
+      </c>
+      <c r="C136" t="s">
+        <v>51</v>
+      </c>
+      <c r="D136" t="s">
+        <v>117</v>
+      </c>
+      <c r="E136">
+        <v>48460</v>
+      </c>
+      <c r="F136" t="s">
+        <v>144</v>
+      </c>
+      <c r="G136" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7">
+      <c r="A137" t="s">
+        <v>7</v>
+      </c>
+      <c r="B137" t="s">
+        <v>12</v>
+      </c>
+      <c r="C137" t="s">
+        <v>51</v>
+      </c>
+      <c r="D137" t="s">
+        <v>117</v>
+      </c>
+      <c r="E137">
+        <v>48460</v>
+      </c>
+      <c r="F137" t="s">
+        <v>144</v>
+      </c>
+      <c r="G137" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7">
+      <c r="A138" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" t="s">
+        <v>12</v>
+      </c>
+      <c r="C138" t="s">
+        <v>51</v>
+      </c>
+      <c r="D138" t="s">
+        <v>117</v>
+      </c>
+      <c r="E138">
+        <v>48460</v>
+      </c>
+      <c r="F138" t="s">
+        <v>144</v>
+      </c>
+      <c r="G138" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7">
+      <c r="A139" t="s">
+        <v>7</v>
+      </c>
+      <c r="B139" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" t="s">
+        <v>52</v>
+      </c>
+      <c r="D139" t="s">
+        <v>118</v>
+      </c>
+      <c r="E139">
+        <v>49700</v>
+      </c>
+      <c r="F139" t="s">
+        <v>144</v>
+      </c>
+      <c r="G139" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7">
+      <c r="A140" t="s">
+        <v>7</v>
+      </c>
+      <c r="B140" t="s">
+        <v>12</v>
+      </c>
+      <c r="C140" t="s">
+        <v>52</v>
+      </c>
+      <c r="D140" t="s">
+        <v>118</v>
+      </c>
+      <c r="E140">
+        <v>49700</v>
+      </c>
+      <c r="F140" t="s">
+        <v>144</v>
+      </c>
+      <c r="G140" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7">
+      <c r="A141" t="s">
+        <v>7</v>
+      </c>
+      <c r="B141" t="s">
+        <v>12</v>
+      </c>
+      <c r="C141" t="s">
+        <v>52</v>
+      </c>
+      <c r="D141" t="s">
+        <v>118</v>
+      </c>
+      <c r="E141">
+        <v>49700</v>
+      </c>
+      <c r="F141" t="s">
+        <v>144</v>
+      </c>
+      <c r="G141" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7">
+      <c r="A142" t="s">
+        <v>7</v>
+      </c>
+      <c r="B142" t="s">
+        <v>12</v>
+      </c>
+      <c r="C142" t="s">
+        <v>52</v>
+      </c>
+      <c r="D142" t="s">
+        <v>118</v>
+      </c>
+      <c r="E142">
+        <v>49700</v>
+      </c>
+      <c r="F142" t="s">
+        <v>144</v>
+      </c>
+      <c r="G142" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7">
+      <c r="A143" t="s">
+        <v>7</v>
+      </c>
+      <c r="B143" t="s">
+        <v>12</v>
+      </c>
+      <c r="C143" t="s">
+        <v>52</v>
+      </c>
+      <c r="D143" t="s">
+        <v>118</v>
+      </c>
+      <c r="E143">
+        <v>49700</v>
+      </c>
+      <c r="F143" t="s">
+        <v>144</v>
+      </c>
+      <c r="G143" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7">
+      <c r="A144" t="s">
+        <v>7</v>
+      </c>
+      <c r="B144" t="s">
+        <v>12</v>
+      </c>
+      <c r="C144" t="s">
+        <v>53</v>
+      </c>
+      <c r="D144" t="s">
+        <v>118</v>
+      </c>
+      <c r="E144">
+        <v>51090</v>
+      </c>
+      <c r="F144" t="s">
+        <v>144</v>
+      </c>
+      <c r="G144" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7">
+      <c r="A145" t="s">
+        <v>7</v>
+      </c>
+      <c r="B145" t="s">
+        <v>12</v>
+      </c>
+      <c r="C145" t="s">
+        <v>53</v>
+      </c>
+      <c r="D145" t="s">
+        <v>118</v>
+      </c>
+      <c r="E145">
+        <v>51090</v>
+      </c>
+      <c r="F145" t="s">
+        <v>144</v>
+      </c>
+      <c r="G145" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" t="s">
+        <v>7</v>
+      </c>
+      <c r="B146" t="s">
+        <v>12</v>
+      </c>
+      <c r="C146" t="s">
+        <v>53</v>
+      </c>
+      <c r="D146" t="s">
+        <v>118</v>
+      </c>
+      <c r="E146">
+        <v>51090</v>
+      </c>
+      <c r="F146" t="s">
+        <v>144</v>
+      </c>
+      <c r="G146" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
+      <c r="A147" t="s">
+        <v>7</v>
+      </c>
+      <c r="B147" t="s">
+        <v>12</v>
+      </c>
+      <c r="C147" t="s">
+        <v>53</v>
+      </c>
+      <c r="D147" t="s">
+        <v>118</v>
+      </c>
+      <c r="E147">
+        <v>51090</v>
+      </c>
+      <c r="F147" t="s">
+        <v>144</v>
+      </c>
+      <c r="G147" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7">
+      <c r="A148" t="s">
+        <v>7</v>
+      </c>
+      <c r="B148" t="s">
+        <v>12</v>
+      </c>
+      <c r="C148" t="s">
+        <v>53</v>
+      </c>
+      <c r="D148" t="s">
+        <v>118</v>
+      </c>
+      <c r="E148">
+        <v>51090</v>
+      </c>
+      <c r="F148" t="s">
+        <v>144</v>
+      </c>
+      <c r="G148" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7">
+      <c r="A149" t="s">
+        <v>7</v>
+      </c>
+      <c r="B149" t="s">
+        <v>12</v>
+      </c>
+      <c r="C149" t="s">
         <v>54</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D149" t="s">
+        <v>118</v>
+      </c>
+      <c r="E149">
+        <v>52660</v>
+      </c>
+      <c r="F149" t="s">
+        <v>144</v>
+      </c>
+      <c r="G149" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7">
+      <c r="A150" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" t="s">
+        <v>12</v>
+      </c>
+      <c r="C150" t="s">
+        <v>54</v>
+      </c>
+      <c r="D150" t="s">
+        <v>118</v>
+      </c>
+      <c r="E150">
+        <v>52660</v>
+      </c>
+      <c r="F150" t="s">
+        <v>144</v>
+      </c>
+      <c r="G150" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7">
+      <c r="A151" t="s">
+        <v>7</v>
+      </c>
+      <c r="B151" t="s">
+        <v>12</v>
+      </c>
+      <c r="C151" t="s">
+        <v>54</v>
+      </c>
+      <c r="D151" t="s">
+        <v>118</v>
+      </c>
+      <c r="E151">
+        <v>52660</v>
+      </c>
+      <c r="F151" t="s">
+        <v>144</v>
+      </c>
+      <c r="G151" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" t="s">
+        <v>7</v>
+      </c>
+      <c r="B152" t="s">
+        <v>12</v>
+      </c>
+      <c r="C152" t="s">
+        <v>54</v>
+      </c>
+      <c r="D152" t="s">
+        <v>118</v>
+      </c>
+      <c r="E152">
+        <v>52660</v>
+      </c>
+      <c r="F152" t="s">
+        <v>144</v>
+      </c>
+      <c r="G152" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7">
+      <c r="A153" t="s">
+        <v>7</v>
+      </c>
+      <c r="B153" t="s">
+        <v>12</v>
+      </c>
+      <c r="C153" t="s">
+        <v>54</v>
+      </c>
+      <c r="D153" t="s">
+        <v>118</v>
+      </c>
+      <c r="E153">
+        <v>52660</v>
+      </c>
+      <c r="F153" t="s">
+        <v>144</v>
+      </c>
+      <c r="G153" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7">
+      <c r="A154" t="s">
+        <v>7</v>
+      </c>
+      <c r="B154" t="s">
+        <v>12</v>
+      </c>
+      <c r="C154" t="s">
+        <v>55</v>
+      </c>
+      <c r="D154" t="s">
+        <v>119</v>
+      </c>
+      <c r="E154">
+        <v>54740</v>
+      </c>
+      <c r="F154" t="s">
+        <v>144</v>
+      </c>
+      <c r="G154" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7">
+      <c r="A155" t="s">
+        <v>7</v>
+      </c>
+      <c r="B155" t="s">
+        <v>12</v>
+      </c>
+      <c r="C155" t="s">
+        <v>55</v>
+      </c>
+      <c r="D155" t="s">
+        <v>119</v>
+      </c>
+      <c r="E155">
+        <v>54740</v>
+      </c>
+      <c r="F155" t="s">
+        <v>144</v>
+      </c>
+      <c r="G155" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7">
+      <c r="A156" t="s">
+        <v>7</v>
+      </c>
+      <c r="B156" t="s">
+        <v>12</v>
+      </c>
+      <c r="C156" t="s">
+        <v>55</v>
+      </c>
+      <c r="D156" t="s">
+        <v>119</v>
+      </c>
+      <c r="E156">
+        <v>54740</v>
+      </c>
+      <c r="F156" t="s">
+        <v>144</v>
+      </c>
+      <c r="G156" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7">
+      <c r="A157" t="s">
+        <v>7</v>
+      </c>
+      <c r="B157" t="s">
+        <v>12</v>
+      </c>
+      <c r="C157" t="s">
+        <v>55</v>
+      </c>
+      <c r="D157" t="s">
+        <v>119</v>
+      </c>
+      <c r="E157">
+        <v>54740</v>
+      </c>
+      <c r="F157" t="s">
+        <v>144</v>
+      </c>
+      <c r="G157" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7">
+      <c r="A158" t="s">
+        <v>7</v>
+      </c>
+      <c r="B158" t="s">
+        <v>12</v>
+      </c>
+      <c r="C158" t="s">
+        <v>55</v>
+      </c>
+      <c r="D158" t="s">
+        <v>119</v>
+      </c>
+      <c r="E158">
+        <v>54740</v>
+      </c>
+      <c r="F158" t="s">
+        <v>144</v>
+      </c>
+      <c r="G158" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7">
+      <c r="A159" t="s">
+        <v>8</v>
+      </c>
+      <c r="B159" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" t="s">
+        <v>56</v>
+      </c>
+      <c r="D159" t="s">
+        <v>120</v>
+      </c>
+      <c r="E159">
+        <v>46320</v>
+      </c>
+      <c r="F159" t="s">
+        <v>144</v>
+      </c>
+      <c r="G159" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7">
+      <c r="A160" t="s">
+        <v>8</v>
+      </c>
+      <c r="B160" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" t="s">
+        <v>57</v>
+      </c>
+      <c r="D160" t="s">
+        <v>121</v>
+      </c>
+      <c r="E160">
+        <v>50500</v>
+      </c>
+      <c r="F160" t="s">
+        <v>144</v>
+      </c>
+      <c r="G160" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7">
+      <c r="A161" t="s">
+        <v>8</v>
+      </c>
+      <c r="B161" t="s">
+        <v>9</v>
+      </c>
+      <c r="C161" t="s">
+        <v>58</v>
+      </c>
+      <c r="D161" t="s">
+        <v>122</v>
+      </c>
+      <c r="E161">
+        <v>50500</v>
+      </c>
+      <c r="F161" t="s">
+        <v>144</v>
+      </c>
+      <c r="G161" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7">
+      <c r="A162" t="s">
+        <v>8</v>
+      </c>
+      <c r="B162" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" t="s">
+        <v>59</v>
+      </c>
+      <c r="D162" t="s">
+        <v>123</v>
+      </c>
+      <c r="E162">
+        <v>52760</v>
+      </c>
+      <c r="F162" t="s">
+        <v>144</v>
+      </c>
+      <c r="G162" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7">
+      <c r="A163" t="s">
+        <v>8</v>
+      </c>
+      <c r="B163" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" t="s">
+        <v>60</v>
+      </c>
+      <c r="D163" t="s">
+        <v>124</v>
+      </c>
+      <c r="E163">
+        <v>52760</v>
+      </c>
+      <c r="F163" t="s">
+        <v>144</v>
+      </c>
+      <c r="G163" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7">
+      <c r="A164" t="s">
+        <v>8</v>
+      </c>
+      <c r="B164" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" t="s">
+        <v>61</v>
+      </c>
+      <c r="D164" t="s">
+        <v>125</v>
+      </c>
+      <c r="E164">
+        <v>55340</v>
+      </c>
+      <c r="F164" t="s">
+        <v>144</v>
+      </c>
+      <c r="G164" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7">
+      <c r="A165" t="s">
+        <v>8</v>
+      </c>
+      <c r="B165" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" t="s">
+        <v>62</v>
+      </c>
+      <c r="D165" t="s">
+        <v>126</v>
+      </c>
+      <c r="E165">
+        <v>61620</v>
+      </c>
+      <c r="F165" t="s">
+        <v>144</v>
+      </c>
+      <c r="G165" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7">
+      <c r="A166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" t="s">
+        <v>63</v>
+      </c>
+      <c r="D166" t="s">
+        <v>127</v>
+      </c>
+      <c r="E166">
+        <v>63130</v>
+      </c>
+      <c r="F166" t="s">
+        <v>144</v>
+      </c>
+      <c r="G166" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7">
+      <c r="A167" t="s">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" t="s">
+        <v>64</v>
+      </c>
+      <c r="D167" t="s">
+        <v>128</v>
+      </c>
+      <c r="E167">
+        <v>67480</v>
+      </c>
+      <c r="F167" t="s">
+        <v>144</v>
+      </c>
+      <c r="G167" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7">
+      <c r="A168" t="s">
+        <v>8</v>
+      </c>
+      <c r="B168" t="s">
+        <v>9</v>
+      </c>
+      <c r="C168" t="s">
+        <v>65</v>
+      </c>
+      <c r="D168" t="s">
+        <v>129</v>
+      </c>
+      <c r="E168">
+        <v>67690</v>
+      </c>
+      <c r="F168" t="s">
+        <v>144</v>
+      </c>
+      <c r="G168" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7">
+      <c r="A169" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>9</v>
+      </c>
+      <c r="C169" t="s">
+        <v>66</v>
+      </c>
+      <c r="D169" t="s">
+        <v>130</v>
+      </c>
+      <c r="E169">
+        <v>69090</v>
+      </c>
+      <c r="F169" t="s">
+        <v>144</v>
+      </c>
+      <c r="G169" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7">
+      <c r="A170" t="s">
+        <v>8</v>
+      </c>
+      <c r="B170" t="s">
+        <v>9</v>
+      </c>
+      <c r="C170" t="s">
+        <v>67</v>
+      </c>
+      <c r="D170" t="s">
+        <v>131</v>
+      </c>
+      <c r="E170">
+        <v>77530</v>
+      </c>
+      <c r="F170" t="s">
+        <v>144</v>
+      </c>
+      <c r="G170" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7">
+      <c r="A171" t="s">
+        <v>8</v>
+      </c>
+      <c r="B171" t="s">
+        <v>9</v>
+      </c>
+      <c r="C171" t="s">
+        <v>68</v>
+      </c>
+      <c r="D171" t="s">
+        <v>132</v>
+      </c>
+      <c r="E171">
+        <v>77650</v>
+      </c>
+      <c r="F171" t="s">
+        <v>144</v>
+      </c>
+      <c r="G171" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7">
+      <c r="A172" t="s">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" t="s">
+        <v>69</v>
+      </c>
+      <c r="D172" t="s">
+        <v>133</v>
+      </c>
+      <c r="E172">
+        <v>82230</v>
+      </c>
+      <c r="F172" t="s">
+        <v>144</v>
+      </c>
+      <c r="G172" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7">
+      <c r="A173" t="s">
+        <v>8</v>
+      </c>
+      <c r="B173" t="s">
+        <v>9</v>
+      </c>
+      <c r="C173" t="s">
+        <v>70</v>
+      </c>
+      <c r="D173" t="s">
+        <v>134</v>
+      </c>
+      <c r="E173">
+        <v>116440</v>
+      </c>
+      <c r="F173" t="s">
+        <v>144</v>
+      </c>
+      <c r="G173" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7">
+      <c r="A174" t="s">
+        <v>8</v>
+      </c>
+      <c r="B174" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" t="s">
+        <v>71</v>
+      </c>
+      <c r="D174" t="s">
+        <v>135</v>
+      </c>
+      <c r="E174">
+        <v>132970</v>
+      </c>
+      <c r="F174" t="s">
+        <v>144</v>
+      </c>
+      <c r="G174" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7">
+      <c r="A175" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" t="s">
+        <v>72</v>
+      </c>
+      <c r="D175" t="s">
+        <v>110</v>
+      </c>
+      <c r="E175">
+        <v>45940</v>
+      </c>
+      <c r="F175" t="s">
+        <v>144</v>
+      </c>
+      <c r="G175" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7">
+      <c r="A176" t="s">
+        <v>8</v>
+      </c>
+      <c r="B176" t="s">
+        <v>11</v>
+      </c>
+      <c r="C176" t="s">
+        <v>72</v>
+      </c>
+      <c r="D176" t="s">
+        <v>110</v>
+      </c>
+      <c r="E176">
+        <v>45940</v>
+      </c>
+      <c r="F176" t="s">
+        <v>144</v>
+      </c>
+      <c r="G176" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7">
+      <c r="A177" t="s">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>73</v>
+      </c>
+      <c r="D177" t="s">
+        <v>110</v>
+      </c>
+      <c r="E177">
+        <v>50460</v>
+      </c>
+      <c r="F177" t="s">
+        <v>144</v>
+      </c>
+      <c r="G177" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7">
+      <c r="A178" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
+        <v>73</v>
+      </c>
+      <c r="D178" t="s">
+        <v>110</v>
+      </c>
+      <c r="E178">
+        <v>50460</v>
+      </c>
+      <c r="F178" t="s">
+        <v>144</v>
+      </c>
+      <c r="G178" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7">
+      <c r="A179" t="s">
+        <v>8</v>
+      </c>
+      <c r="B179" t="s">
+        <v>11</v>
+      </c>
+      <c r="C179" t="s">
+        <v>74</v>
+      </c>
+      <c r="D179" t="s">
+        <v>110</v>
+      </c>
+      <c r="E179">
+        <v>56310</v>
+      </c>
+      <c r="F179" t="s">
+        <v>144</v>
+      </c>
+      <c r="G179" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7">
+      <c r="A180" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180" t="s">
+        <v>11</v>
+      </c>
+      <c r="C180" t="s">
+        <v>74</v>
+      </c>
+      <c r="D180" t="s">
+        <v>110</v>
+      </c>
+      <c r="E180">
+        <v>56310</v>
+      </c>
+      <c r="F180" t="s">
+        <v>144</v>
+      </c>
+      <c r="G180" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7">
+      <c r="A181" t="s">
+        <v>8</v>
+      </c>
+      <c r="B181" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" t="s">
+        <v>75</v>
+      </c>
+      <c r="D181" t="s">
+        <v>110</v>
+      </c>
+      <c r="E181">
+        <v>71190</v>
+      </c>
+      <c r="F181" t="s">
+        <v>144</v>
+      </c>
+      <c r="G181" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7">
+      <c r="A182" t="s">
+        <v>8</v>
+      </c>
+      <c r="B182" t="s">
+        <v>11</v>
+      </c>
+      <c r="C182" t="s">
+        <v>75</v>
+      </c>
+      <c r="D182" t="s">
+        <v>110</v>
+      </c>
+      <c r="E182">
+        <v>71190</v>
+      </c>
+      <c r="F182" t="s">
+        <v>144</v>
+      </c>
+      <c r="G182" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7">
+      <c r="A183" t="s">
+        <v>8</v>
+      </c>
+      <c r="B183" t="s">
+        <v>11</v>
+      </c>
+      <c r="C183" t="s">
+        <v>76</v>
+      </c>
+      <c r="D183" t="s">
+        <v>110</v>
+      </c>
+      <c r="E183">
+        <v>79490</v>
+      </c>
+      <c r="F183" t="s">
+        <v>144</v>
+      </c>
+      <c r="G183" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7">
+      <c r="A184" t="s">
+        <v>8</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" t="s">
+        <v>76</v>
+      </c>
+      <c r="D184" t="s">
+        <v>110</v>
+      </c>
+      <c r="E184">
+        <v>79490</v>
+      </c>
+      <c r="F184" t="s">
+        <v>144</v>
+      </c>
+      <c r="G184" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7">
+      <c r="A185" t="s">
+        <v>8</v>
+      </c>
+      <c r="B185" t="s">
+        <v>11</v>
+      </c>
+      <c r="C185" t="s">
+        <v>77</v>
+      </c>
+      <c r="D185" t="s">
+        <v>110</v>
+      </c>
+      <c r="E185">
+        <v>86240</v>
+      </c>
+      <c r="F185" t="s">
+        <v>144</v>
+      </c>
+      <c r="G185" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7">
+      <c r="A186" t="s">
+        <v>8</v>
+      </c>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" t="s">
+        <v>77</v>
+      </c>
+      <c r="D186" t="s">
+        <v>110</v>
+      </c>
+      <c r="E186">
+        <v>86240</v>
+      </c>
+      <c r="F186" t="s">
+        <v>144</v>
+      </c>
+      <c r="G186" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7">
+      <c r="A187" t="s">
+        <v>8</v>
+      </c>
+      <c r="B187" t="s">
+        <v>12</v>
+      </c>
+      <c r="C187" t="s">
+        <v>78</v>
+      </c>
+      <c r="D187" t="s">
+        <v>136</v>
+      </c>
+      <c r="E187">
+        <v>47390</v>
+      </c>
+      <c r="F187" t="s">
+        <v>144</v>
+      </c>
+      <c r="G187" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7">
+      <c r="A188" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" t="s">
+        <v>12</v>
+      </c>
+      <c r="C188" t="s">
+        <v>78</v>
+      </c>
+      <c r="D188" t="s">
+        <v>136</v>
+      </c>
+      <c r="E188">
+        <v>47390</v>
+      </c>
+      <c r="F188" t="s">
+        <v>144</v>
+      </c>
+      <c r="G188" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7">
+      <c r="A189" t="s">
+        <v>8</v>
+      </c>
+      <c r="B189" t="s">
+        <v>12</v>
+      </c>
+      <c r="C189" t="s">
+        <v>79</v>
+      </c>
+      <c r="D189" t="s">
+        <v>137</v>
+      </c>
+      <c r="E189">
+        <v>47540</v>
+      </c>
+      <c r="F189" t="s">
+        <v>144</v>
+      </c>
+      <c r="G189" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7">
+      <c r="A190" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>12</v>
+      </c>
+      <c r="C190" t="s">
+        <v>79</v>
+      </c>
+      <c r="D190" t="s">
+        <v>137</v>
+      </c>
+      <c r="E190">
+        <v>47540</v>
+      </c>
+      <c r="F190" t="s">
+        <v>144</v>
+      </c>
+      <c r="G190" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7">
+      <c r="A191" t="s">
+        <v>8</v>
+      </c>
+      <c r="B191" t="s">
+        <v>12</v>
+      </c>
+      <c r="C191" t="s">
+        <v>80</v>
+      </c>
+      <c r="D191" t="s">
+        <v>138</v>
+      </c>
+      <c r="E191">
+        <v>47720</v>
+      </c>
+      <c r="F191" t="s">
+        <v>144</v>
+      </c>
+      <c r="G191" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7">
+      <c r="A192" t="s">
+        <v>8</v>
+      </c>
+      <c r="B192" t="s">
+        <v>12</v>
+      </c>
+      <c r="C192" t="s">
+        <v>80</v>
+      </c>
+      <c r="D192" t="s">
+        <v>138</v>
+      </c>
+      <c r="E192">
+        <v>47720</v>
+      </c>
+      <c r="F192" t="s">
+        <v>144</v>
+      </c>
+      <c r="G192" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" t="s">
+        <v>8</v>
+      </c>
+      <c r="B193" t="s">
+        <v>12</v>
+      </c>
+      <c r="C193" t="s">
+        <v>81</v>
+      </c>
+      <c r="D193" t="s">
+        <v>138</v>
+      </c>
+      <c r="E193">
+        <v>47840</v>
+      </c>
+      <c r="F193" t="s">
+        <v>144</v>
+      </c>
+      <c r="G193" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" t="s">
+        <v>8</v>
+      </c>
+      <c r="B194" t="s">
+        <v>12</v>
+      </c>
+      <c r="C194" t="s">
+        <v>81</v>
+      </c>
+      <c r="D194" t="s">
+        <v>138</v>
+      </c>
+      <c r="E194">
+        <v>47840</v>
+      </c>
+      <c r="F194" t="s">
+        <v>144</v>
+      </c>
+      <c r="G194" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" t="s">
+        <v>8</v>
+      </c>
+      <c r="B195" t="s">
+        <v>12</v>
+      </c>
+      <c r="C195" t="s">
+        <v>82</v>
+      </c>
+      <c r="D195" t="s">
+        <v>139</v>
+      </c>
+      <c r="E195">
+        <v>48450</v>
+      </c>
+      <c r="F195" t="s">
+        <v>144</v>
+      </c>
+      <c r="G195" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" t="s">
+        <v>8</v>
+      </c>
+      <c r="B196" t="s">
+        <v>12</v>
+      </c>
+      <c r="C196" t="s">
+        <v>82</v>
+      </c>
+      <c r="D196" t="s">
+        <v>139</v>
+      </c>
+      <c r="E196">
+        <v>48450</v>
+      </c>
+      <c r="F196" t="s">
+        <v>144</v>
+      </c>
+      <c r="G196" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7">
+      <c r="A197" t="s">
+        <v>8</v>
+      </c>
+      <c r="B197" t="s">
+        <v>12</v>
+      </c>
+      <c r="C197" t="s">
+        <v>83</v>
+      </c>
+      <c r="D197" t="s">
+        <v>140</v>
+      </c>
+      <c r="E197">
+        <v>49640</v>
+      </c>
+      <c r="F197" t="s">
+        <v>144</v>
+      </c>
+      <c r="G197" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7">
+      <c r="A198" t="s">
+        <v>8</v>
+      </c>
+      <c r="B198" t="s">
+        <v>12</v>
+      </c>
+      <c r="C198" t="s">
+        <v>83</v>
+      </c>
+      <c r="D198" t="s">
+        <v>140</v>
+      </c>
+      <c r="E198">
+        <v>49640</v>
+      </c>
+      <c r="F198" t="s">
+        <v>144</v>
+      </c>
+      <c r="G198" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7">
+      <c r="A199" t="s">
+        <v>8</v>
+      </c>
+      <c r="B199" t="s">
+        <v>12</v>
+      </c>
+      <c r="C199" t="s">
         <v>84</v>
       </c>
-      <c r="E86">
-        <v>54740</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="D199" t="s">
+        <v>140</v>
+      </c>
+      <c r="E199">
+        <v>49800</v>
+      </c>
+      <c r="F199" t="s">
+        <v>144</v>
+      </c>
+      <c r="G199" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>8</v>
+      </c>
+      <c r="B200" t="s">
+        <v>12</v>
+      </c>
+      <c r="C200" t="s">
+        <v>84</v>
+      </c>
+      <c r="D200" t="s">
+        <v>140</v>
+      </c>
+      <c r="E200">
+        <v>49800</v>
+      </c>
+      <c r="F200" t="s">
+        <v>144</v>
+      </c>
+      <c r="G200" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7">
+      <c r="A201" t="s">
+        <v>8</v>
+      </c>
+      <c r="B201" t="s">
+        <v>12</v>
+      </c>
+      <c r="C201" t="s">
         <v>85</v>
       </c>
-      <c r="G86" t="s">
-        <v>170</v>
+      <c r="D201" t="s">
+        <v>141</v>
+      </c>
+      <c r="E201">
+        <v>51060</v>
+      </c>
+      <c r="F201" t="s">
+        <v>144</v>
+      </c>
+      <c r="G201" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>8</v>
+      </c>
+      <c r="B202" t="s">
+        <v>12</v>
+      </c>
+      <c r="C202" t="s">
+        <v>85</v>
+      </c>
+      <c r="D202" t="s">
+        <v>141</v>
+      </c>
+      <c r="E202">
+        <v>51060</v>
+      </c>
+      <c r="F202" t="s">
+        <v>144</v>
+      </c>
+      <c r="G202" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7">
+      <c r="A203" t="s">
+        <v>8</v>
+      </c>
+      <c r="B203" t="s">
+        <v>12</v>
+      </c>
+      <c r="C203" t="s">
+        <v>86</v>
+      </c>
+      <c r="D203" t="s">
+        <v>141</v>
+      </c>
+      <c r="E203">
+        <v>52500</v>
+      </c>
+      <c r="F203" t="s">
+        <v>144</v>
+      </c>
+      <c r="G203" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7">
+      <c r="A204" t="s">
+        <v>8</v>
+      </c>
+      <c r="B204" t="s">
+        <v>12</v>
+      </c>
+      <c r="C204" t="s">
+        <v>86</v>
+      </c>
+      <c r="D204" t="s">
+        <v>141</v>
+      </c>
+      <c r="E204">
+        <v>52500</v>
+      </c>
+      <c r="F204" t="s">
+        <v>144</v>
+      </c>
+      <c r="G204" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7">
+      <c r="A205" t="s">
+        <v>8</v>
+      </c>
+      <c r="B205" t="s">
+        <v>12</v>
+      </c>
+      <c r="C205" t="s">
+        <v>87</v>
+      </c>
+      <c r="D205" t="s">
+        <v>141</v>
+      </c>
+      <c r="E205">
+        <v>54110</v>
+      </c>
+      <c r="F205" t="s">
+        <v>144</v>
+      </c>
+      <c r="G205" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7">
+      <c r="A206" t="s">
+        <v>8</v>
+      </c>
+      <c r="B206" t="s">
+        <v>12</v>
+      </c>
+      <c r="C206" t="s">
+        <v>87</v>
+      </c>
+      <c r="D206" t="s">
+        <v>141</v>
+      </c>
+      <c r="E206">
+        <v>54110</v>
+      </c>
+      <c r="F206" t="s">
+        <v>144</v>
+      </c>
+      <c r="G206" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7">
+      <c r="A207" t="s">
+        <v>8</v>
+      </c>
+      <c r="B207" t="s">
+        <v>12</v>
+      </c>
+      <c r="C207" t="s">
+        <v>88</v>
+      </c>
+      <c r="D207" t="s">
+        <v>142</v>
+      </c>
+      <c r="E207">
+        <v>56240</v>
+      </c>
+      <c r="F207" t="s">
+        <v>144</v>
+      </c>
+      <c r="G207" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7">
+      <c r="A208" t="s">
+        <v>8</v>
+      </c>
+      <c r="B208" t="s">
+        <v>12</v>
+      </c>
+      <c r="C208" t="s">
+        <v>88</v>
+      </c>
+      <c r="D208" t="s">
+        <v>142</v>
+      </c>
+      <c r="E208">
+        <v>56240</v>
+      </c>
+      <c r="F208" t="s">
+        <v>144</v>
+      </c>
+      <c r="G208" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" t="s">
+        <v>8</v>
+      </c>
+      <c r="B209" t="s">
+        <v>12</v>
+      </c>
+      <c r="C209" t="s">
+        <v>89</v>
+      </c>
+      <c r="D209" t="s">
+        <v>143</v>
+      </c>
+      <c r="E209">
+        <v>62300</v>
+      </c>
+      <c r="F209" t="s">
+        <v>144</v>
+      </c>
+      <c r="G209" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7">
+      <c r="A210" t="s">
+        <v>8</v>
+      </c>
+      <c r="B210" t="s">
+        <v>12</v>
+      </c>
+      <c r="C210" t="s">
+        <v>89</v>
+      </c>
+      <c r="D210" t="s">
+        <v>143</v>
+      </c>
+      <c r="E210">
+        <v>62300</v>
+      </c>
+      <c r="F210" t="s">
+        <v>144</v>
+      </c>
+      <c r="G210" t="s">
+        <v>353</v>
       </c>
     </row>
   </sheetData>
